--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_Decimal/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_Decimal/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R65ffc34655484ef5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8b0e023d2fe14979"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_Decimal/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_Decimal/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8b0e023d2fe14979"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0a6d9ea870864b53"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_Decimal/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_Decimal/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0a6d9ea870864b53"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R268edad6457a46ca"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_Decimal/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_Decimal/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R268edad6457a46ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0fe9443f7c904746"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_Decimal/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_Decimal/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0fe9443f7c904746"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R177ca7ce6e5b44ad"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_Decimal/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_Decimal/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R177ca7ce6e5b44ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R67845240146241f9"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_Decimal/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_Decimal/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R67845240146241f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd5b988c0e9404fbb"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_Decimal/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_Decimal/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd5b988c0e9404fbb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4f23017528aa4bf1"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_Decimal/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_Decimal/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4f23017528aa4bf1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R02cc6d85734f4492"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_Decimal/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_Decimal/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R02cc6d85734f4492"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8c1c02f1aa16473f"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_Decimal/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_Decimal/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8c1c02f1aa16473f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R997472ae387a4637"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_Decimal/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_Decimal/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R997472ae387a4637"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6adbd4d755e74d07"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_Decimal/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_Decimal/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6adbd4d755e74d07"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R03a7e178a5f944e7"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_Decimal/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_Decimal/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R03a7e178a5f944e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re58c1f558f734c75"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_Decimal/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_Decimal/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re58c1f558f734c75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1bf71f999e074902"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_Decimal/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_Decimal/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1bf71f999e074902"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbb53440ed533488c"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_Decimal/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_Decimal/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbb53440ed533488c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9d675aa0ffeb45cc"/>
   </x:sheets>
 </x:workbook>
 </file>
